--- a/ALL/p13-out/START.xlsx
+++ b/ALL/p13-out/START.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Titles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Titles" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,13 +413,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>used</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>used_at</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>used_project</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>easy pizza</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-04-30 12:41:55</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New site (p13)</t>
         </is>
       </c>
     </row>

--- a/ALL/p13-out/START.xlsx
+++ b/ALL/p13-out/START.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>easy pizza</t>
+          <t>Crispy Oven Baked Chicken Tacos</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-30 12:41:55</t>
+          <t>2026-05-08 14:43:25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
